--- a/tables/tableLoadDriver.xlsx
+++ b/tables/tableLoadDriver.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23001"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godovova\MATLAB_Godovova\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\greatuniter\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56399143-F84F-4D02-A45E-6786D33D621E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3615" yWindow="2745" windowWidth="19185" windowHeight="9000" tabRatio="861" activeTab="1"/>
+    <workbookView xWindow="-16770" yWindow="1410" windowWidth="14400" windowHeight="10755" tabRatio="861" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -21,7 +22,6 @@
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,51 +29,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
-    <t>ФИО проверяющего</t>
+    <t>BoardNumber</t>
   </si>
   <si>
-    <t>Комментарий по проверке</t>
+    <t>DeviceType</t>
   </si>
   <si>
-    <t>текст комментария</t>
+    <t>Designation</t>
   </si>
   <si>
-    <t>Фамилия И.О.</t>
+    <t>SerialNumber</t>
   </si>
   <si>
-    <t>Смещение диапазона</t>
+    <t>Comment</t>
   </si>
   <si>
-    <t>Напряжение, В</t>
+    <t>InspectorName</t>
   </si>
   <si>
-    <t>Значение на ЦАП</t>
+    <t>OffsetHighRangeFromEEPROM</t>
   </si>
   <si>
-    <t>Смещение внесено в EEPROM</t>
+    <t>Voltage_mV</t>
   </si>
   <si>
-    <t>Номер платы</t>
+    <t>DAC</t>
   </si>
   <si>
-    <t>Тип устройства</t>
+    <t>load driver</t>
   </si>
   <si>
-    <t>драйвер нагрузки</t>
-  </si>
-  <si>
-    <t>да</t>
-  </si>
-  <si>
-    <t>Выходной ток, А</t>
+    <t>Current_mA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -163,7 +157,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -178,9 +172,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -198,8 +189,8 @@
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Стиль 1" xfId="1"/>
-    <cellStyle name="Стиль 2" xfId="2"/>
+    <cellStyle name="Стиль 1" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Стиль 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -253,7 +244,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="Стиль таблицы 1" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Стиль таблицы 1" pivot="0" count="2">
+    <tableStyle name="Стиль таблицы 1" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
@@ -531,7 +522,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="E10:J12"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -581,22 +572,22 @@
       </c>
     </row>
     <row r="12" spans="5:10" x14ac:dyDescent="0.25">
-      <c r="E12" s="7">
+      <c r="E12" s="6">
         <v>750</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>1023</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="6">
         <v>1024</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="6">
         <v>1250</v>
       </c>
-      <c r="I12" s="7">
+      <c r="I12" s="6">
         <v>1500</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="6">
         <v>1600</v>
       </c>
     </row>
@@ -606,8 +597,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BT60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:BT61"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.140625" style="1" customWidth="1"/>
@@ -617,172 +608,29 @@
   <sheetData>
     <row r="1" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="8">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="B1" s="7"/>
     </row>
     <row r="2" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-      <c r="AA2" s="3"/>
-      <c r="AB2" s="3"/>
-      <c r="AC2" s="3"/>
-      <c r="AD2" s="3"/>
-      <c r="AE2" s="3"/>
-      <c r="AF2" s="3"/>
-      <c r="AG2" s="3"/>
-      <c r="AH2" s="3"/>
-      <c r="AI2" s="3"/>
-      <c r="AJ2" s="3"/>
-      <c r="AK2" s="3"/>
-      <c r="AL2" s="3"/>
-      <c r="AM2" s="3"/>
-      <c r="AN2" s="3"/>
-      <c r="AO2" s="3"/>
-      <c r="AP2" s="3"/>
-      <c r="AQ2" s="3"/>
-      <c r="AR2" s="3"/>
-      <c r="AS2" s="3"/>
-      <c r="AT2" s="3"/>
-      <c r="AU2" s="3"/>
-      <c r="AV2" s="3"/>
-      <c r="AW2" s="3"/>
-      <c r="AX2" s="3"/>
-      <c r="AY2" s="3"/>
-      <c r="AZ2" s="3"/>
-      <c r="BA2" s="3"/>
-      <c r="BB2" s="3"/>
-      <c r="BC2" s="3"/>
-      <c r="BD2" s="3"/>
-      <c r="BE2" s="3"/>
-      <c r="BF2" s="3"/>
-      <c r="BG2" s="3"/>
-      <c r="BH2" s="3"/>
-      <c r="BI2" s="3"/>
-      <c r="BJ2" s="3"/>
-      <c r="BK2" s="3"/>
-      <c r="BL2" s="3"/>
-      <c r="BM2" s="3"/>
-      <c r="BN2" s="3"/>
-      <c r="BO2" s="3"/>
-      <c r="BP2" s="3"/>
-      <c r="BQ2" s="3"/>
-      <c r="BR2" s="3"/>
     </row>
     <row r="3" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
-      <c r="V3" s="3"/>
-      <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="3"/>
-      <c r="AA3" s="3"/>
-      <c r="AB3" s="3"/>
-      <c r="AC3" s="3"/>
-      <c r="AD3" s="3"/>
-      <c r="AE3" s="3"/>
-      <c r="AF3" s="3"/>
-      <c r="AG3" s="3"/>
-      <c r="AH3" s="3"/>
-      <c r="AI3" s="3"/>
-      <c r="AJ3" s="3"/>
-      <c r="AK3" s="3"/>
-      <c r="AL3" s="3"/>
-      <c r="AM3" s="3"/>
-      <c r="AN3" s="3"/>
-      <c r="AO3" s="3"/>
-      <c r="AP3" s="3"/>
-      <c r="AQ3" s="3"/>
-      <c r="AR3" s="3"/>
-      <c r="AS3" s="3"/>
-      <c r="AT3" s="3"/>
-      <c r="AU3" s="3"/>
-      <c r="AV3" s="3"/>
-      <c r="AW3" s="3"/>
-      <c r="AX3" s="3"/>
-      <c r="AY3" s="3"/>
-      <c r="AZ3" s="3"/>
-      <c r="BA3" s="3"/>
-      <c r="BB3" s="3"/>
-      <c r="BC3" s="3"/>
-      <c r="BD3" s="3"/>
-      <c r="BE3" s="3"/>
-      <c r="BF3" s="3"/>
-      <c r="BG3" s="3"/>
-      <c r="BH3" s="3"/>
-      <c r="BI3" s="3"/>
-      <c r="BJ3" s="3"/>
-      <c r="BK3" s="3"/>
-      <c r="BL3" s="3"/>
-      <c r="BM3" s="3"/>
-      <c r="BN3" s="3"/>
-      <c r="BO3" s="3"/>
-      <c r="BP3" s="3"/>
-      <c r="BQ3" s="3"/>
-      <c r="BR3" s="3"/>
+      <c r="B3" s="8"/>
     </row>
     <row r="4" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="4"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -853,12 +701,10 @@
     </row>
     <row r="5" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -929,11 +775,9 @@
     </row>
     <row r="6" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <v>0</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B6" s="7"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1005,35 +849,19 @@
     </row>
     <row r="7" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
       </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0</v>
-      </c>
-      <c r="E7" s="2">
-        <v>0</v>
-      </c>
-      <c r="F7" s="2">
-        <v>0</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0</v>
-      </c>
-      <c r="H7" s="2">
-        <v>0</v>
-      </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
-      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -1097,7 +925,7 @@
     </row>
     <row r="8" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2">
         <v>0</v>
@@ -1189,36 +1017,36 @@
     </row>
     <row r="9" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="7">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2">
         <v>0</v>
       </c>
-      <c r="C9" s="7">
-        <v>250</v>
-      </c>
-      <c r="D9" s="7">
-        <v>500</v>
-      </c>
-      <c r="E9" s="7">
-        <v>750</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1023</v>
-      </c>
-      <c r="G9" s="7">
-        <v>1024</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1250</v>
-      </c>
-      <c r="I9" s="7">
-        <v>1500</v>
-      </c>
-      <c r="J9" s="7">
-        <v>1600</v>
-      </c>
-      <c r="K9" s="2"/>
+      <c r="C9" s="2">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>0</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1278,20 +1106,39 @@
       <c r="BP9" s="3"/>
       <c r="BQ9" s="3"/>
       <c r="BR9" s="3"/>
-      <c r="BS9" s="2"/>
-      <c r="BT9" s="2"/>
-    </row>
-    <row r="10" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+    </row>
+    <row r="10" spans="1:72" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6">
+        <v>0</v>
+      </c>
+      <c r="C10" s="6">
+        <v>250</v>
+      </c>
+      <c r="D10" s="6">
+        <v>500</v>
+      </c>
+      <c r="E10" s="6">
+        <v>750</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1023</v>
+      </c>
+      <c r="G10" s="6">
+        <v>1024</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1250</v>
+      </c>
+      <c r="I10" s="6">
+        <v>1500</v>
+      </c>
+      <c r="J10" s="6">
+        <v>1600</v>
+      </c>
+      <c r="K10" s="2"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -2519,6 +2366,8 @@
       <c r="BP26" s="3"/>
       <c r="BQ26" s="3"/>
       <c r="BR26" s="3"/>
+      <c r="BS26" s="2"/>
+      <c r="BT26" s="2"/>
     </row>
     <row r="27" spans="2:72" x14ac:dyDescent="0.25">
       <c r="B27" s="3"/>
@@ -4934,6 +4783,77 @@
       <c r="BQ60" s="3"/>
       <c r="BR60" s="3"/>
     </row>
+    <row r="61" spans="2:70" x14ac:dyDescent="0.25">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+      <c r="D61" s="3"/>
+      <c r="E61" s="3"/>
+      <c r="F61" s="3"/>
+      <c r="G61" s="3"/>
+      <c r="H61" s="3"/>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="3"/>
+      <c r="L61" s="3"/>
+      <c r="M61" s="3"/>
+      <c r="N61" s="3"/>
+      <c r="O61" s="3"/>
+      <c r="P61" s="3"/>
+      <c r="Q61" s="3"/>
+      <c r="R61" s="3"/>
+      <c r="S61" s="3"/>
+      <c r="T61" s="3"/>
+      <c r="U61" s="3"/>
+      <c r="V61" s="3"/>
+      <c r="W61" s="3"/>
+      <c r="X61" s="3"/>
+      <c r="Y61" s="3"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
+      <c r="AB61" s="3"/>
+      <c r="AC61" s="3"/>
+      <c r="AD61" s="3"/>
+      <c r="AE61" s="3"/>
+      <c r="AF61" s="3"/>
+      <c r="AG61" s="3"/>
+      <c r="AH61" s="3"/>
+      <c r="AI61" s="3"/>
+      <c r="AJ61" s="3"/>
+      <c r="AK61" s="3"/>
+      <c r="AL61" s="3"/>
+      <c r="AM61" s="3"/>
+      <c r="AN61" s="3"/>
+      <c r="AO61" s="3"/>
+      <c r="AP61" s="3"/>
+      <c r="AQ61" s="3"/>
+      <c r="AR61" s="3"/>
+      <c r="AS61" s="3"/>
+      <c r="AT61" s="3"/>
+      <c r="AU61" s="3"/>
+      <c r="AV61" s="3"/>
+      <c r="AW61" s="3"/>
+      <c r="AX61" s="3"/>
+      <c r="AY61" s="3"/>
+      <c r="AZ61" s="3"/>
+      <c r="BA61" s="3"/>
+      <c r="BB61" s="3"/>
+      <c r="BC61" s="3"/>
+      <c r="BD61" s="3"/>
+      <c r="BE61" s="3"/>
+      <c r="BF61" s="3"/>
+      <c r="BG61" s="3"/>
+      <c r="BH61" s="3"/>
+      <c r="BI61" s="3"/>
+      <c r="BJ61" s="3"/>
+      <c r="BK61" s="3"/>
+      <c r="BL61" s="3"/>
+      <c r="BM61" s="3"/>
+      <c r="BN61" s="3"/>
+      <c r="BO61" s="3"/>
+      <c r="BP61" s="3"/>
+      <c r="BQ61" s="3"/>
+      <c r="BR61" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
